--- a/doc/Diccionario_features.xlsx
+++ b/doc/Diccionario_features.xlsx
@@ -5,22 +5,24 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\No_Country\6ta_simulacion_Retencion_de_clientes\Retencion-de-clientes---NoCountry\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A6016D9-5FB0-4DAE-8CFE-01AE310F0E90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F90C257-F57A-4B63-9DEA-6890B44685C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Diccionario_feature" sheetId="1" r:id="rId1"/>
+    <sheet name="fichero churn" sheetId="1" r:id="rId1"/>
+    <sheet name="fichero churn1" sheetId="2" r:id="rId2"/>
+    <sheet name="fichero churn_data" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="122">
   <si>
     <t>Nombre de la columna</t>
   </si>
@@ -182,13 +184,414 @@
   </si>
   <si>
     <t>Puntos por riesgo de abandono (Del 1 al 5)</t>
+  </si>
+  <si>
+    <t>Nombre de la Columna</t>
+  </si>
+  <si>
+    <t>Tipo de Dato</t>
+  </si>
+  <si>
+    <t>RowNumber</t>
+  </si>
+  <si>
+    <t>Número de fila o índice del registro. No tiene significado analítico, solo identifica la posición.</t>
+  </si>
+  <si>
+    <t>CustomerId</t>
+  </si>
+  <si>
+    <t>Identificador único del cliente dentro del sistema bancario.</t>
+  </si>
+  <si>
+    <t>Surname</t>
+  </si>
+  <si>
+    <t>string (object)</t>
+  </si>
+  <si>
+    <t>Apellido del cliente.</t>
+  </si>
+  <si>
+    <t>CreditScore</t>
+  </si>
+  <si>
+    <t>Puntuación crediticia del cliente (valor entre 300 y 850 aproximadamente). Mide el riesgo crediticio.</t>
+  </si>
+  <si>
+    <t>Geography</t>
+  </si>
+  <si>
+    <t>País o región de residencia del cliente.</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>Género del cliente.</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Edad del cliente en años.</t>
+  </si>
+  <si>
+    <t>Tenure</t>
+  </si>
+  <si>
+    <t>Antigüedad del cliente en el banco (en años).</t>
+  </si>
+  <si>
+    <t>Balance</t>
+  </si>
+  <si>
+    <t>Saldo actual del cliente en su cuenta bancaria.</t>
+  </si>
+  <si>
+    <t>NumOfProducts</t>
+  </si>
+  <si>
+    <t>Cantidad de productos bancarios contratados (por ejemplo, cuentas, tarjetas, préstamos).</t>
+  </si>
+  <si>
+    <t>HasCrCard</t>
+  </si>
+  <si>
+    <t>IsActiveMember</t>
+  </si>
+  <si>
+    <t>EstimatedSalary</t>
+  </si>
+  <si>
+    <t>Estimación del salario anual del cliente.</t>
+  </si>
+  <si>
+    <t>Exited</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>nps_score</t>
+  </si>
+  <si>
+    <t>tx_count_30d</t>
+  </si>
+  <si>
+    <t>avg_tx_amount</t>
+  </si>
+  <si>
+    <t>failed_tx</t>
+  </si>
+  <si>
+    <t>support_tickets</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Indica si el cliente posee una tarjeta de crédito. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Sí / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> No</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Indica si el cliente es considerado activo en el banco (por frecuencia de uso o transacciones). </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Sí / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> No</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Variable objetivo: indica si el cliente abandonó el banco (churn). </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Sí (se fue) / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> No (permanece)</t>
+    </r>
+  </si>
+  <si>
+    <t>Edad del usuario en años.</t>
+  </si>
+  <si>
+    <t>Género del usuario.</t>
+  </si>
+  <si>
+    <t>Identificador único de seguridad asignado al usuario.</t>
+  </si>
+  <si>
+    <t>Tipo o categoría de la región donde reside el usuario.</t>
+  </si>
+  <si>
+    <t>Categoría de membresía del usuario dentro del sistema.</t>
+  </si>
+  <si>
+    <t>string / datetime</t>
+  </si>
+  <si>
+    <t>Fecha de alta o registro del usuario en la plataforma.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Indica si el usuario se unió mediante una referencia. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Yes / No / ? (Desconocido)</t>
+    </r>
+  </si>
+  <si>
+    <t>Código de referencia usado al unirse (si corresponde).</t>
+  </si>
+  <si>
+    <t>Tipo de ofertas preferidas por el usuario.</t>
+  </si>
+  <si>
+    <t>Medio principal usado para operar en la plataforma (p. ej. Desktop, Smartphone).</t>
+  </si>
+  <si>
+    <t>Tipo de conexión a internet usada para acceder al servicio.</t>
+  </si>
+  <si>
+    <t>string / time</t>
+  </si>
+  <si>
+    <t>Hora del último acceso registrado en la plataforma.</t>
+  </si>
+  <si>
+    <t>Días transcurridos desde el último inicio de sesión.</t>
+  </si>
+  <si>
+    <t>Tiempo promedio (en segundos o minutos) que el usuario pasa en la plataforma por sesión.</t>
+  </si>
+  <si>
+    <t>Valor monetario promedio de las transacciones realizadas por el usuario.</t>
+  </si>
+  <si>
+    <t>Frecuencia promedio de inicio de sesión (en días).</t>
+  </si>
+  <si>
+    <t>Cantidad de puntos acumulados en la billetera del usuario.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Indica si el usuario utilizó algún descuento especial. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Yes / No</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Indica si el usuario suele aplicar ofertas o promociones. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Yes / No</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Indica si el usuario realizó alguna queja en el pasado. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Yes / No</t>
+    </r>
+  </si>
+  <si>
+    <t>Estado actual de la queja del usuario (si existe).</t>
+  </si>
+  <si>
+    <t>Comentario o categoría de feedback proporcionado por el usuario.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Puntuación de riesgo de abandono (churn) estimada. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Valores más altos = mayor riesgo.</t>
+    </r>
+  </si>
+  <si>
+    <t>Cantidad de transacciones realizadas por el usuario en los últimos 30 días.</t>
+  </si>
+  <si>
+    <t>Monto promedio de las transacciones realizadas.</t>
+  </si>
+  <si>
+    <t>Número de transacciones fallidas.</t>
+  </si>
+  <si>
+    <t>Cantidad de tickets de soporte abiertos por el usuario.</t>
+  </si>
+  <si>
+    <t>Puntuación NPS (Net Promoter Score), mide la satisfacción o lealtad del cliente.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -206,8 +609,61 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -226,8 +682,26 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -250,11 +724,122 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -265,11 +850,280 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="11">
+    <dxf>
+      <font>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -297,9 +1151,9 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Diccionario_feature-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="headerRow" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="secondRowStripe" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="10"/>
+      <tableStyleElement type="firstRowStripe" dxfId="9"/>
+      <tableStyleElement type="secondRowStripe" dxfId="8"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -319,6 +1173,17 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Nombre de la columna"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Descripción"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Tipo de dato"/>
+  </tableColumns>
+  <tableStyleInfo name="Diccionario_feature-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{747A9680-D164-4906-BBF0-575C1B96E77F}" name="Table_13" displayName="Table_13" ref="A1:C29" headerRowDxfId="4" dataDxfId="0" totalsRowDxfId="5" headerRowBorderDxfId="6" tableBorderDxfId="7">
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{25F606B6-F0B2-4A18-9E3A-701849CEBE1E}" name="Nombre de la Columna" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{EEE55066-E8AD-4265-A303-2B93C9569104}" name="Tipo de Dato" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{5CBC4F00-B7E2-40FB-A680-237F35966F21}" name="Descripción" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="Diccionario_feature-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -545,7 +1410,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
@@ -556,7 +1421,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
@@ -567,7 +1432,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
@@ -578,7 +1443,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>11</v>
       </c>
@@ -589,7 +1454,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>13</v>
       </c>
@@ -600,7 +1465,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>15</v>
       </c>
@@ -611,7 +1476,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>17</v>
       </c>
@@ -622,7 +1487,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>19</v>
       </c>
@@ -633,7 +1498,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
@@ -644,7 +1509,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>23</v>
       </c>
@@ -655,7 +1520,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>25</v>
       </c>
@@ -666,7 +1531,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>27</v>
       </c>
@@ -677,7 +1542,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>29</v>
       </c>
@@ -688,7 +1553,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>31</v>
       </c>
@@ -699,7 +1564,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>33</v>
       </c>
@@ -710,7 +1575,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>36</v>
       </c>
@@ -721,7 +1586,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>38</v>
       </c>
@@ -732,7 +1597,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>40</v>
       </c>
@@ -743,7 +1608,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>42</v>
       </c>
@@ -754,7 +1619,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>44</v>
       </c>
@@ -817,4 +1682,627 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA6C2701-711A-41CE-BE17-F2E9F5B09573}">
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="26.140625" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" style="13" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="10"/>
+    </row>
+    <row r="2" spans="1:4" ht="99.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2" s="11"/>
+    </row>
+    <row r="3" spans="1:4" ht="57" x14ac:dyDescent="0.2">
+      <c r="A3" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D3" s="11"/>
+    </row>
+    <row r="4" spans="1:4" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="11"/>
+    </row>
+    <row r="5" spans="1:4" ht="99.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5" s="11"/>
+    </row>
+    <row r="6" spans="1:4" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="11"/>
+    </row>
+    <row r="7" spans="1:4" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" s="11"/>
+    </row>
+    <row r="8" spans="1:4" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8" s="11"/>
+    </row>
+    <row r="9" spans="1:4" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A9" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D9" s="11"/>
+    </row>
+    <row r="10" spans="1:4" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D10" s="11"/>
+    </row>
+    <row r="11" spans="1:4" ht="99.75" x14ac:dyDescent="0.2">
+      <c r="A11" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D11" s="11"/>
+    </row>
+    <row r="12" spans="1:4" ht="58.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D12" s="11"/>
+    </row>
+    <row r="13" spans="1:4" ht="101.25" x14ac:dyDescent="0.2">
+      <c r="A13" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" s="11"/>
+    </row>
+    <row r="14" spans="1:4" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A14" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D14" s="11"/>
+    </row>
+    <row r="15" spans="1:4" ht="87" x14ac:dyDescent="0.2">
+      <c r="A15" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" s="11"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EF095E0-0FEF-4640-9957-8FC48E8B6093}">
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A2" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+    </row>
+    <row r="3" spans="1:6" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="D3" s="15"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+    </row>
+    <row r="4" spans="1:6" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="D4" s="17"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+    </row>
+    <row r="5" spans="1:6" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="D5" s="15"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+    </row>
+    <row r="6" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A6" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" s="15"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+    </row>
+    <row r="7" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A7" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="D7" s="15"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+    </row>
+    <row r="8" spans="1:6" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="D8" s="15"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+    </row>
+    <row r="9" spans="1:6" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A9" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="D9" s="15"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+    </row>
+    <row r="10" spans="1:6" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A10" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="D10" s="15"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+    </row>
+    <row r="11" spans="1:6" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="D11" s="15"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+    </row>
+    <row r="12" spans="1:6" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A12" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D12" s="15"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+    </row>
+    <row r="13" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A13" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="D13" s="15"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+    </row>
+    <row r="14" spans="1:6" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A14" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="D14" s="15"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+    </row>
+    <row r="15" spans="1:6" ht="102" x14ac:dyDescent="0.2">
+      <c r="A15" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="D15" s="15"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+    </row>
+    <row r="16" spans="1:6" ht="89.25" x14ac:dyDescent="0.2">
+      <c r="A16" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="D16" s="15"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+    </row>
+    <row r="17" spans="1:6" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A17" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="D17" s="15"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+    </row>
+    <row r="18" spans="1:6" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A18" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="D18" s="15"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+    </row>
+    <row r="19" spans="1:6" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="A19" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="D19" s="15"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+    </row>
+    <row r="20" spans="1:6" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A20" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="D20" s="15"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+    </row>
+    <row r="21" spans="1:6" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A21" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="D21" s="15"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+    </row>
+    <row r="22" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A22" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="D22" s="15"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+    </row>
+    <row r="23" spans="1:6" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A23" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="D23" s="15"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+    </row>
+    <row r="24" spans="1:6" ht="102" x14ac:dyDescent="0.2">
+      <c r="A24" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="D24" s="15"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+    </row>
+    <row r="25" spans="1:6" ht="89.25" x14ac:dyDescent="0.2">
+      <c r="A25" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="B25" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="D25" s="15"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+    </row>
+    <row r="26" spans="1:6" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="A26" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="B26" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="D26" s="15"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+    </row>
+    <row r="27" spans="1:6" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A27" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="B27" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="D27" s="15"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+    </row>
+    <row r="28" spans="1:6" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A28" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="D28" s="15"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+    </row>
+    <row r="29" spans="1:6" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A29" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="D29" s="15"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D30" s="15"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>